--- a/MU/Test upload format/Normal/2026 - 2027/Q2 26-27.xlsx
+++ b/MU/Test upload format/Normal/2026 - 2027/Q2 26-27.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>Q2CR701</t>
+    <t>Q2CR1501</t>
   </si>
   <si>
     <t>900000</t>
@@ -215,7 +215,7 @@
     <t>SBIN0001234</t>
   </si>
   <si>
-    <t>Q2CR702</t>
+    <t>Q2CR1502</t>
   </si>
   <si>
     <t>800000</t>
@@ -233,7 +233,7 @@
     <t>CR703</t>
   </si>
   <si>
-    <t>Q2CR703</t>
+    <t>Q2CR1503</t>
   </si>
   <si>
     <t>500000</t>
@@ -251,7 +251,7 @@
     <t>CR704</t>
   </si>
   <si>
-    <t>Q2CR704</t>
+    <t>Q2CR1504</t>
   </si>
   <si>
     <t>100000</t>
@@ -260,49 +260,49 @@
     <t>CR705</t>
   </si>
   <si>
-    <t>Q2CR705</t>
+    <t>Q2CR1505</t>
   </si>
   <si>
     <t>CR706</t>
   </si>
   <si>
-    <t>Q2CR706</t>
+    <t>Q2CR1506</t>
   </si>
   <si>
     <t>CR707</t>
   </si>
   <si>
-    <t>Q2CR707</t>
+    <t>Q2CR1507</t>
   </si>
   <si>
     <t>CR708</t>
   </si>
   <si>
-    <t>Q2CR708</t>
+    <t>Q2CR1508</t>
   </si>
   <si>
     <t>CR709</t>
   </si>
   <si>
-    <t>Q2CR709</t>
+    <t>Q2CR1509</t>
   </si>
   <si>
     <t>CR710</t>
   </si>
   <si>
-    <t>Q2CR710</t>
+    <t>Q2CR1510</t>
   </si>
   <si>
     <t>CR711</t>
   </si>
   <si>
-    <t>Q2CR711</t>
+    <t>Q2CR1511</t>
   </si>
   <si>
     <t>CR712</t>
   </si>
   <si>
-    <t>Q2CR712</t>
+    <t>Q2CR1512</t>
   </si>
   <si>
     <t>01-08-2026</t>
@@ -311,19 +311,19 @@
     <t>CR713</t>
   </si>
   <si>
-    <t>Q2CR713</t>
+    <t>Q2CR1513</t>
   </si>
   <si>
     <t>CR714</t>
   </si>
   <si>
-    <t>Q2CR714</t>
+    <t>Q2CR1514</t>
   </si>
   <si>
     <t>CR715</t>
   </si>
   <si>
-    <t>Q2CR715</t>
+    <t>Q2CR1515</t>
   </si>
   <si>
     <t>3</t>
@@ -332,7 +332,7 @@
     <t>CR716</t>
   </si>
   <si>
-    <t>Q2CR716</t>
+    <t>Q2CR1516</t>
   </si>
   <si>
     <t>4</t>
@@ -341,7 +341,7 @@
     <t>CR717</t>
   </si>
   <si>
-    <t>Q2CR717</t>
+    <t>Q2CR1517</t>
   </si>
   <si>
     <t>TP</t>
@@ -350,7 +350,7 @@
     <t>CR718</t>
   </si>
   <si>
-    <t>Q2CR718</t>
+    <t>Q2CR1518</t>
   </si>
   <si>
     <t>1000000</t>
@@ -362,7 +362,7 @@
     <t>CR719</t>
   </si>
   <si>
-    <t>Q2CR719</t>
+    <t>Q2CR1519</t>
   </si>
   <si>
     <t>10-08-2026</t>
@@ -371,31 +371,31 @@
     <t>CR720</t>
   </si>
   <si>
-    <t>Q2CR720</t>
+    <t>Q2CR1520</t>
   </si>
   <si>
     <t>CR721</t>
   </si>
   <si>
-    <t>Q2CR721</t>
+    <t>Q2CR1521</t>
   </si>
   <si>
     <t>CR722</t>
   </si>
   <si>
-    <t>Q2CR722</t>
+    <t>Q2CR1522</t>
   </si>
   <si>
     <t>CR723</t>
   </si>
   <si>
-    <t>Q2CR723</t>
+    <t>Q2CR1523</t>
   </si>
   <si>
     <t>CR724</t>
   </si>
   <si>
-    <t>Q2CR724</t>
+    <t>Q2CR1524</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AO25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -1560,7 +1560,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
+    <row r="2" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
+    <row r="3" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A3" s="10" t="s">
         <v>57</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:41">
+    <row r="4" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A4" s="10" t="s">
         <v>65</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:41">
+    <row r="5" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A5" s="10" t="s">
         <v>41</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:41">
+    <row r="6" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A6" s="10" t="s">
         <v>57</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:41">
+    <row r="7" s="2" customFormat="1" hidden="1" spans="1:41">
       <c r="A7" s="10" t="s">
         <v>65</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:41">
+    <row r="8" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A8" s="13" t="s">
         <v>41</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:41">
+    <row r="9" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:41">
+    <row r="10" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A10" s="13" t="s">
         <v>65</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:41">
+    <row r="11" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:41">
+    <row r="12" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A12" s="13" t="s">
         <v>57</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:41">
+    <row r="13" s="3" customFormat="1" hidden="1" spans="1:41">
       <c r="A13" s="13" t="s">
         <v>65</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" spans="1:41">
+    <row r="14" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A14" s="15" t="s">
         <v>41</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" spans="1:41">
+    <row r="15" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A15" s="15" t="s">
         <v>57</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" s="4" customFormat="1" spans="1:41">
+    <row r="16" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" s="4" customFormat="1" spans="1:41">
+    <row r="17" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A17" s="15" t="s">
         <v>41</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1" spans="1:41">
+    <row r="18" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A18" s="15" t="s">
         <v>57</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" s="4" customFormat="1" spans="1:41">
+    <row r="19" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A19" s="15" t="s">
         <v>104</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" s="4" customFormat="1" spans="1:41">
+    <row r="25" s="4" customFormat="1" hidden="1" spans="1:41">
       <c r="A25" s="15" t="s">
         <v>65</v>
       </c>
@@ -4238,6 +4238,15 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK25" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="16">
+      <filters>
+        <filter val="Q2CR1520"/>
+        <filter val="Q2CR1521"/>
+        <filter val="Q2CR1522"/>
+        <filter val="Q2CR1523"/>
+        <filter val="Q2CR1519"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
